--- a/src/cart/elliptic/optimization/cart__elliptic_operator_ip__mp_apply_ci.xlsx
+++ b/src/cart/elliptic/optimization/cart__elliptic_operator_ip__mp_apply_ci.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11213"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joerg/Numerics/HiSPEET-Fusion/src/cart/elliptic/taurus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joerg/Numerics/HiSPEET-Fusion/src/cart/elliptic/optimization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813A6FF3-3691-F949-AAE2-BA5E3CCAAB54}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C699C4-C2A4-F34B-A625-58CAC903B8BB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5040" yWindow="500" windowWidth="20620" windowHeight="15280" xr2:uid="{FA8EC70F-FD05-134D-8027-15CCBCA4C043}"/>
+    <workbookView minimized="1" xWindow="520" yWindow="500" windowWidth="23940" windowHeight="18780" xr2:uid="{FA8EC70F-FD05-134D-8027-15CCBCA4C043}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="36">
   <si>
     <t>S</t>
   </si>
@@ -33,9 +33,6 @@
     <t>E %</t>
   </si>
   <si>
-    <t>time/DOF in ms</t>
-  </si>
-  <si>
     <t>– SetArray</t>
   </si>
   <si>
@@ -121,6 +118,21 @@
   </si>
   <si>
     <t>2,5 GHz?</t>
+  </si>
+  <si>
+    <t>v6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenMP barriers reduced </t>
+  </si>
+  <si>
+    <t>MPI with 8 processes</t>
+  </si>
+  <si>
+    <t>time/DOF in s</t>
+  </si>
+  <si>
+    <t>Threads</t>
   </si>
 </sst>
 </file>
@@ -156,12 +168,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -176,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -214,6 +232,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -528,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD71264-5964-A74F-B487-33D0E857939E}">
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="15.83203125" style="6" customWidth="1"/>
@@ -538,54 +568,54 @@
     <col min="14" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="6">
         <f>16^3</f>
         <v>4096</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="6">
         <f>(B1+1)^3 * B2</f>
         <v>16777216</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="D4" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>0</v>
@@ -594,10 +624,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>5.582E-8</v>
       </c>
@@ -609,8 +642,11 @@
         <f>100*B9/1</f>
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>2.9639999999999999E-8</v>
       </c>
@@ -622,8 +658,11 @@
         <f>100*B10/2</f>
         <v>94.163292847503371</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>1.5980000000000001E-8</v>
       </c>
@@ -635,8 +674,11 @@
         <f>100*B11/4</f>
         <v>87.327909887359183</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>9.7049999999999999E-9</v>
       </c>
@@ -648,8 +690,11 @@
         <f>100*B12/8</f>
         <v>71.89592993302422</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>7.9669999999999995E-9</v>
       </c>
@@ -661,10 +706,13 @@
         <f>100*B13/12</f>
         <v>58.386678381657674</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>0</v>
@@ -673,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>3.6629999999999998E-8</v>
       </c>
@@ -746,7 +794,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>0</v>
@@ -755,7 +803,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
@@ -825,7 +873,7 @@
     </row>
     <row r="29" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>0</v>
@@ -834,7 +882,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -969,7 +1017,7 @@
     </row>
     <row r="36" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>0</v>
@@ -978,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
@@ -1048,7 +1096,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>0</v>
@@ -1057,7 +1105,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43" s="12"/>
     </row>
@@ -1128,7 +1176,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>0</v>
@@ -1137,7 +1185,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E50" s="12"/>
     </row>
@@ -1208,7 +1256,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>0</v>
@@ -1217,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E57" s="12"/>
     </row>
@@ -1234,7 +1282,7 @@
         <v>100</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -1264,14 +1312,14 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="5">
+      <c r="A61" s="18">
         <v>1.839E-9</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="15">
         <f t="shared" si="5"/>
         <v>7.248504622077216</v>
       </c>
-      <c r="C61" s="8">
+      <c r="C61" s="16">
         <f>100*B61/8</f>
         <v>90.606307775965206</v>
       </c>
@@ -1289,34 +1337,105 @@
         <v>77.898550724637673</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="5"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="13"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="5">
+        <v>1.3399999999999999E-8</v>
+      </c>
+      <c r="B65" s="7"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="13"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="5">
+        <v>6.809E-9</v>
+      </c>
+      <c r="B66" s="7"/>
+      <c r="C66" s="8"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="5">
+        <v>3.4649999999999999E-9</v>
+      </c>
+      <c r="B67" s="7"/>
+      <c r="C67" s="8"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="17">
+        <v>1.8110000000000001E-9</v>
+      </c>
+      <c r="B68" s="7"/>
+      <c r="C68" s="8"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="5">
+        <v>1.4269999999999999E-9</v>
+      </c>
+      <c r="B69" s="7"/>
+      <c r="C69" s="8"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="5"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="8"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="17">
+        <v>1.842E-9</v>
+      </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" s="6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C67" s="14" t="s">
-        <v>13</v>
+      <c r="C75" s="14" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
